--- a/InputData/trans/ICtPSFfL/Incremental Cost to Produce Substitute Fuel for LCFS.xlsx
+++ b/InputData/trans/ICtPSFfL/Incremental Cost to Produce Substitute Fuel for LCFS.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28521"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipL\InputData\trans\ICtPSFfL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreazafra/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7F2BAE-595A-4E40-8624-7B647AD0C9D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13800"/>
+    <workbookView xWindow="34400" yWindow="5240" windowWidth="28800" windowHeight="13800" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="2" r:id="rId1"/>
@@ -28,10 +29,21 @@
     <definedName name="nonlignite_multiplier">#REF!</definedName>
     <definedName name="use_lifecycle_biofuel_EIs">[1]About!$A$61</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -39,6 +51,69 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="43">
+  <si>
+    <t>ICtPSFfL Incremental Cost to Produce Substitute Fuel for LCFS</t>
+  </si>
+  <si>
+    <t>Source:</t>
+  </si>
+  <si>
+    <t>Fuel Production Costs</t>
+  </si>
+  <si>
+    <t>E3 Pathways</t>
+  </si>
+  <si>
+    <t>Weighted Average Delivered Energy Costs</t>
+  </si>
+  <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>This varibale calculates the incremental fuel production cost from switching from</t>
+  </si>
+  <si>
+    <t xml:space="preserve">conventional fuels to LCFS substitute fuels. In Pathways, conventional ethanol </t>
+  </si>
+  <si>
+    <t>has the same price as gasoline, so it has no incremental cost. Electricity credits</t>
+  </si>
+  <si>
+    <t>are typically delivered to electric charging station owners, and there is no incremental</t>
+  </si>
+  <si>
+    <t>cost of electricity production. Similarly, in Pathways the delivered natural gas prices</t>
+  </si>
+  <si>
+    <t>are all below the gasoline price, so we use a value of zero. Only renewable diesel,</t>
+  </si>
+  <si>
+    <t>which we use as the substitute fuel for petroleum diesel, has an incremental cost</t>
+  </si>
+  <si>
+    <t>increase. Note also that per Pathways, this value drops over time, eventually falling so far</t>
+  </si>
+  <si>
+    <t>that it costs lets than traditional diesel to produce, though we limit our incremental</t>
+  </si>
+  <si>
+    <t>costs to a low value of zero.</t>
+  </si>
+  <si>
+    <t>Conventional fuels under the LCFS (petroleum gasoline, petroleum diesel, and</t>
+  </si>
+  <si>
+    <t>jet fuel) should always have a value of zero in this variable.</t>
+  </si>
+  <si>
+    <t>Conversion Factor</t>
+  </si>
+  <si>
+    <t>BTU/GJ</t>
+  </si>
+  <si>
+    <t>$/GJ</t>
+  </si>
   <si>
     <t>Renewable Diesel</t>
   </si>
@@ -67,13 +142,13 @@
     <t>$/BTU</t>
   </si>
   <si>
-    <t>BTU/GJ</t>
-  </si>
-  <si>
     <t>Reference Fuels</t>
   </si>
   <si>
     <t>electricity</t>
+  </si>
+  <si>
+    <t>petroleum gasoline</t>
   </si>
   <si>
     <t>natural gas</t>
@@ -85,76 +160,16 @@
     <t>biofuel diesel</t>
   </si>
   <si>
-    <t>petroleum gasoline</t>
-  </si>
-  <si>
     <t>petroleum diesel</t>
   </si>
   <si>
     <t>Incremental Costs of Production ($/BTU)</t>
   </si>
   <si>
-    <t>$/GJ</t>
+    <t>Cost ($/BTU)</t>
   </si>
   <si>
     <t>jet fuel</t>
-  </si>
-  <si>
-    <t>Weighted Average Delivered Energy Costs</t>
-  </si>
-  <si>
-    <t>E3 Pathways</t>
-  </si>
-  <si>
-    <t>Fuel Production Costs</t>
-  </si>
-  <si>
-    <t>Source:</t>
-  </si>
-  <si>
-    <t>Notes:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">conventional fuels to LCFS substitute fuels. In Pathways, conventional ethanol </t>
-  </si>
-  <si>
-    <t>has the same price as gasoline, so it has no incremental cost. Electricity credits</t>
-  </si>
-  <si>
-    <t>are typically delivered to electric charging station owners, and there is no incremental</t>
-  </si>
-  <si>
-    <t>cost of electricity production. Similarly, in Pathways the delivered natural gas prices</t>
-  </si>
-  <si>
-    <t>are all below the gasoline price, so we use a value of zero. Only renewable diesel,</t>
-  </si>
-  <si>
-    <t>which we use as the substitute fuel for petroleum diesel, has an incremental cost</t>
-  </si>
-  <si>
-    <t>increase. Note also that per Pathways, this value drops over time, eventually falling so far</t>
-  </si>
-  <si>
-    <t>costs to a low value of zero.</t>
-  </si>
-  <si>
-    <t>that it costs lets than traditional diesel to produce, though we limit our incremental</t>
-  </si>
-  <si>
-    <t>This varibale calculates the incremental fuel production cost from switching from</t>
-  </si>
-  <si>
-    <t>Conversion Factor</t>
-  </si>
-  <si>
-    <t>jet fuel) should always have a value of zero in this variable.</t>
-  </si>
-  <si>
-    <t>Conventional fuels under the LCFS (petroleum gasoline, petroleum diesel, and</t>
-  </si>
-  <si>
-    <t>ICtPSFfL Incremental Cost to Produce Substitute Fuel for LCFS</t>
   </si>
   <si>
     <t>heavy or residual fuel oil</t>
@@ -165,15 +180,12 @@
   <si>
     <t>hydrogen</t>
   </si>
-  <si>
-    <t>Cost ($/BTU)</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -216,10 +228,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -243,7 +254,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="About"/>
@@ -272,18 +283,7 @@
       <sheetName val="PEI-IFPEI"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="61">
-          <cell r="A61" t="b">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="160">
-          <cell r="A160" t="b">
-            <v>1</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
@@ -574,117 +574,117 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="54" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>22</v>
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="B4" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="5">
+    <row r="5" spans="1:2">
+      <c r="B5" s="4">
         <v>2018</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="B6" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
+    <row r="24" spans="1:2">
+      <c r="A24" s="2">
         <v>947817.12</v>
       </c>
       <c r="B24" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -694,20 +694,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AK35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.42578125" customWidth="1"/>
     <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>18</v>
+    <row r="1" spans="1:37" s="3" customFormat="1">
+      <c r="A1" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:37">
       <c r="B2">
         <v>2015</v>
       </c>
@@ -817,9 +817,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:37">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="B3">
         <v>30.8367260296898</v>
@@ -930,9 +930,9 @@
         <v>38.8994534841326</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:37">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>30.978814519130498</v>
@@ -1043,15 +1043,15 @@
         <v>47.526138928681398</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:37">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D5">
         <v>20.2922337992403</v>
@@ -1072,13 +1072,13 @@
         <v>22.145680536501199</v>
       </c>
       <c r="J5" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="K5" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="L5" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="M5">
         <v>21.3964771206401</v>
@@ -1156,15 +1156,15 @@
         <v>36.031200708728697</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D6">
         <v>32.527466640073698</v>
@@ -1206,72 +1206,72 @@
         <v>33.997588461072702</v>
       </c>
       <c r="Q6" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="R6" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="S6" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="T6" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="U6" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="V6" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="W6" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="X6" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="Y6" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="Z6" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="AA6" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="AB6" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="AC6" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="AD6" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="AE6" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="AF6" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="AG6" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="AH6" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="AI6" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="AJ6" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="AK6">
         <v>41.934834775512002</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:37">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="B7">
         <v>15.357264235821001</v>
@@ -1282,7 +1282,7 @@
       <c r="D7">
         <v>18.885450227945402</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7">
         <v>19.0133949371196</v>
       </c>
       <c r="F7">
@@ -1382,9 +1382,9 @@
         <v>36.031508112322399</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:37">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="B8">
         <v>16.6352636486229</v>
@@ -1495,14 +1495,14 @@
         <v>39.309585492238803</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:37">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:37">
       <c r="A10" t="s">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="B10">
         <v>30.8367260296898</v>
@@ -1613,9 +1613,9 @@
         <v>38.8994534841326</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:37">
       <c r="A11" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="B11">
         <v>30.978814519130498</v>
@@ -1726,14 +1726,14 @@
         <v>47.526138928681398</v>
       </c>
     </row>
-    <row r="13" spans="1:37" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>8</v>
+    <row r="13" spans="1:37" s="3" customFormat="1">
+      <c r="A13" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:37">
       <c r="A14" t="s">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="B14">
         <f t="shared" ref="B14:AK14" si="0">B3/btu_per_EJ</f>
@@ -1880,9 +1880,9 @@
         <v>4.1041096075720387E-5</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:37">
       <c r="A15" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="B15">
         <f t="shared" ref="B15:AK15" si="1">B4/btu_per_EJ</f>
@@ -2029,9 +2029,9 @@
         <v>5.0142731045712066E-5</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:37">
       <c r="A16" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="B16" t="e">
         <f t="shared" ref="B16:AK16" si="2">B5/btu_per_EJ</f>
@@ -2178,9 +2178,9 @@
         <v>3.8014929197236589E-5</v>
       </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:37">
       <c r="A17" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B17" t="e">
         <f t="shared" ref="B17:AK17" si="3">B6/btu_per_EJ</f>
@@ -2327,9 +2327,9 @@
         <v>4.4243592873182117E-5</v>
       </c>
     </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:37">
       <c r="A18" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="B18">
         <f t="shared" ref="B18:AK18" si="4">B7/btu_per_EJ</f>
@@ -2476,9 +2476,9 @@
         <v>3.8015253525197351E-5</v>
       </c>
     </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:37">
       <c r="A19" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="B19">
         <f t="shared" ref="B19:AK19" si="5">B8/btu_per_EJ</f>
@@ -2625,9 +2625,9 @@
         <v>4.1473808251362669E-5</v>
       </c>
     </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:37">
       <c r="A20" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="B20">
         <f t="shared" ref="B20:AK20" si="6">B9/btu_per_EJ</f>
@@ -2774,9 +2774,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:37">
       <c r="A21" t="s">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="B21">
         <f t="shared" ref="B21:AK21" si="7">B10/btu_per_EJ</f>
@@ -2923,9 +2923,9 @@
         <v>4.1041096075720387E-5</v>
       </c>
     </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:37">
       <c r="A22" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="B22">
         <f t="shared" ref="B22:AK22" si="8">B11/btu_per_EJ</f>
@@ -3072,49 +3072,49 @@
         <v>5.0142731045712066E-5</v>
       </c>
     </row>
-    <row r="24" spans="1:37" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>10</v>
+    <row r="24" spans="1:37" s="3" customFormat="1">
+      <c r="A24" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:37">
       <c r="A25" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:37">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:37">
       <c r="A27" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:37">
       <c r="A28" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="30" spans="1:37" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>17</v>
+    <row r="30" spans="1:37" s="3" customFormat="1">
+      <c r="A30" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:37">
       <c r="B31">
         <v>2015</v>
       </c>
@@ -3224,9 +3224,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="32" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:37">
       <c r="A32" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -3337,9 +3337,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:37">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -3450,9 +3450,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:37">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="B34">
         <f>0</f>
@@ -3599,9 +3599,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:37">
       <c r="A35" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="B35">
         <f>B21-B19</f>
@@ -3754,20 +3754,20 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AK11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:BE11"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.85546875" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:57">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B1">
         <v>2015</v>
@@ -3877,10 +3877,70 @@
       <c r="AK1">
         <v>2050</v>
       </c>
+      <c r="AL1">
+        <v>2051</v>
+      </c>
+      <c r="AM1">
+        <v>2052</v>
+      </c>
+      <c r="AN1">
+        <v>2053</v>
+      </c>
+      <c r="AO1">
+        <v>2054</v>
+      </c>
+      <c r="AP1">
+        <v>2055</v>
+      </c>
+      <c r="AQ1">
+        <v>2056</v>
+      </c>
+      <c r="AR1">
+        <v>2057</v>
+      </c>
+      <c r="AS1">
+        <v>2058</v>
+      </c>
+      <c r="AT1">
+        <v>2059</v>
+      </c>
+      <c r="AU1">
+        <v>2060</v>
+      </c>
+      <c r="AV1">
+        <v>2061</v>
+      </c>
+      <c r="AW1">
+        <v>2062</v>
+      </c>
+      <c r="AX1">
+        <v>2063</v>
+      </c>
+      <c r="AY1">
+        <v>2064</v>
+      </c>
+      <c r="AZ1">
+        <v>2065</v>
+      </c>
+      <c r="BA1">
+        <v>2066</v>
+      </c>
+      <c r="BB1">
+        <v>2067</v>
+      </c>
+      <c r="BC1">
+        <v>2068</v>
+      </c>
+      <c r="BD1">
+        <v>2069</v>
+      </c>
+      <c r="BE1">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:57">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="B2">
         <f>Calcs!B32</f>
@@ -4026,10 +4086,90 @@
         <f>Calcs!AK32</f>
         <v>0</v>
       </c>
+      <c r="AL2">
+        <f>Calcs!AL32</f>
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <f>Calcs!AM32</f>
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <f>Calcs!AN32</f>
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <f>Calcs!AO32</f>
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <f>Calcs!AP32</f>
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <f>Calcs!AQ32</f>
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <f>Calcs!AR32</f>
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <f>Calcs!AS32</f>
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <f>Calcs!AT32</f>
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <f>Calcs!AU32</f>
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <f>Calcs!AV32</f>
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <f>Calcs!AW32</f>
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <f>Calcs!AX32</f>
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <f>Calcs!AY32</f>
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <f>Calcs!AZ32</f>
+        <v>0</v>
+      </c>
+      <c r="BA2">
+        <f>Calcs!BA32</f>
+        <v>0</v>
+      </c>
+      <c r="BB2">
+        <f>Calcs!BB32</f>
+        <v>0</v>
+      </c>
+      <c r="BC2">
+        <f>Calcs!BC32</f>
+        <v>0</v>
+      </c>
+      <c r="BD2">
+        <f>Calcs!BD32</f>
+        <v>0</v>
+      </c>
+      <c r="BE2">
+        <f>Calcs!BE32</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:57">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B3">
         <f>Calcs!B33</f>
@@ -4175,10 +4315,90 @@
         <f>Calcs!AK33</f>
         <v>0</v>
       </c>
+      <c r="AL3">
+        <f>Calcs!AL33</f>
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <f>Calcs!AM33</f>
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <f>Calcs!AN33</f>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <f>Calcs!AO33</f>
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <f>Calcs!AP33</f>
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <f>Calcs!AQ33</f>
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <f>Calcs!AR33</f>
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <f>Calcs!AS33</f>
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <f>Calcs!AT33</f>
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <f>Calcs!AU33</f>
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <f>Calcs!AV33</f>
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <f>Calcs!AW33</f>
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <f>Calcs!AX33</f>
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <f>Calcs!AY33</f>
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <f>Calcs!AZ33</f>
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <f>Calcs!BA33</f>
+        <v>0</v>
+      </c>
+      <c r="BB3">
+        <f>Calcs!BB33</f>
+        <v>0</v>
+      </c>
+      <c r="BC3">
+        <f>Calcs!BC33</f>
+        <v>0</v>
+      </c>
+      <c r="BD3">
+        <f>Calcs!BD33</f>
+        <v>0</v>
+      </c>
+      <c r="BE3">
+        <f>Calcs!BE33</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:57">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="B4">
         <f>0</f>
@@ -4324,10 +4544,90 @@
         <f>0</f>
         <v>0</v>
       </c>
+      <c r="AL4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BD4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BE4">
+        <f>0</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:57">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="B5">
         <f>0</f>
@@ -4473,10 +4773,90 @@
         <f>0</f>
         <v>0</v>
       </c>
+      <c r="AL5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <f>0</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:57">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="B6">
         <f>Calcs!B34</f>
@@ -4622,10 +5002,90 @@
         <f>Calcs!AK34</f>
         <v>0</v>
       </c>
+      <c r="AL6">
+        <f>Calcs!AL34</f>
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <f>Calcs!AM34</f>
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <f>Calcs!AN34</f>
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <f>Calcs!AO34</f>
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <f>Calcs!AP34</f>
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <f>Calcs!AQ34</f>
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <f>Calcs!AR34</f>
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <f>Calcs!AS34</f>
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <f>Calcs!AT34</f>
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <f>Calcs!AU34</f>
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <f>Calcs!AV34</f>
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <f>Calcs!AW34</f>
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <f>Calcs!AX34</f>
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <f>Calcs!AY34</f>
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <f>Calcs!AZ34</f>
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <f>Calcs!BA34</f>
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <f>Calcs!BB34</f>
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <f>Calcs!BC34</f>
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <f>Calcs!BD34</f>
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <f>Calcs!BE34</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:57">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="B7">
         <f>MAX(Calcs!B35,0)</f>
@@ -4771,10 +5231,90 @@
         <f>MAX(Calcs!AK35,0)</f>
         <v>0</v>
       </c>
+      <c r="AL7">
+        <f>MAX(Calcs!AL35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <f>MAX(Calcs!AM35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <f>MAX(Calcs!AN35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <f>MAX(Calcs!AO35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <f>MAX(Calcs!AP35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <f>MAX(Calcs!AQ35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <f>MAX(Calcs!AR35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <f>MAX(Calcs!AS35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <f>MAX(Calcs!AT35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <f>MAX(Calcs!AU35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <f>MAX(Calcs!AV35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <f>MAX(Calcs!AW35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <f>MAX(Calcs!AX35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <f>MAX(Calcs!AY35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <f>MAX(Calcs!AZ35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <f>MAX(Calcs!BA35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <f>MAX(Calcs!BB35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <f>MAX(Calcs!BC35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <f>MAX(Calcs!BD35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <f>MAX(Calcs!BE35,0)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:57">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="B8">
         <f>0</f>
@@ -4920,10 +5460,90 @@
         <f>0</f>
         <v>0</v>
       </c>
+      <c r="AL8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <f>0</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:57">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9">
         <f>0</f>
@@ -5069,10 +5689,90 @@
         <f>0</f>
         <v>0</v>
       </c>
+      <c r="AL9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AW9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BB9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BC9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BD9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BE9">
+        <f>0</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:57">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B10">
         <f>0</f>
@@ -5218,10 +5918,90 @@
         <f>0</f>
         <v>0</v>
       </c>
+      <c r="AL10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BC10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BD10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BE10">
+        <f>0</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:57">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11">
         <f>0</f>
@@ -5364,6 +6144,86 @@
         <v>0</v>
       </c>
       <c r="AK11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AV11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AX11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AY11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AZ11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BA11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BB11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BC11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BD11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BE11">
         <f>0</f>
         <v>0</v>
       </c>
@@ -5371,4 +6231,175 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
+    <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="79748b23-d81a-423e-9112-21109dc864e6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AE162E8-EE01-49E1-A128-F73A722F801C}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F34DFC44-17E7-479F-8633-1016098F3609}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3B532D6-B0CC-4365-B1E6-AC8F590DA96B}"/>
 </file>